--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395861</v>
+        <v>121395864</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78246</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447523</v>
+        <v>447448</v>
       </c>
       <c r="R2" t="n">
-        <v>6729097</v>
+        <v>6728823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395864</v>
+        <v>121395852</v>
       </c>
       <c r="B4" t="n">
-        <v>78246</v>
+        <v>90697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447448</v>
+        <v>447606</v>
       </c>
       <c r="R4" t="n">
-        <v>6728823</v>
+        <v>6729038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395852</v>
+        <v>121395861</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447606</v>
+        <v>447523</v>
       </c>
       <c r="R5" t="n">
-        <v>6729038</v>
+        <v>6729097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395864</v>
+        <v>121395852</v>
       </c>
       <c r="B2" t="n">
-        <v>78246</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447448</v>
+        <v>447606</v>
       </c>
       <c r="R2" t="n">
-        <v>6728823</v>
+        <v>6729038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395852</v>
+        <v>121395861</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447606</v>
+        <v>447523</v>
       </c>
       <c r="R4" t="n">
-        <v>6729038</v>
+        <v>6729097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395861</v>
+        <v>121395864</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78246</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447523</v>
+        <v>447448</v>
       </c>
       <c r="R5" t="n">
-        <v>6729097</v>
+        <v>6728823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395852</v>
+        <v>121395864</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>78249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447606</v>
+        <v>447448</v>
       </c>
       <c r="R2" t="n">
-        <v>6729038</v>
+        <v>6728823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>121395847</v>
       </c>
       <c r="B3" t="n">
-        <v>79190</v>
+        <v>79193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395861</v>
+        <v>121395852</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447523</v>
+        <v>447606</v>
       </c>
       <c r="R4" t="n">
-        <v>6729097</v>
+        <v>6729038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395864</v>
+        <v>121395861</v>
       </c>
       <c r="B5" t="n">
-        <v>78246</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447448</v>
+        <v>447523</v>
       </c>
       <c r="R5" t="n">
-        <v>6728823</v>
+        <v>6729097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395864</v>
+        <v>121395852</v>
       </c>
       <c r="B2" t="n">
-        <v>78249</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447448</v>
+        <v>447606</v>
       </c>
       <c r="R2" t="n">
-        <v>6728823</v>
+        <v>6729038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395852</v>
+        <v>121395864</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>78249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447606</v>
+        <v>447448</v>
       </c>
       <c r="R4" t="n">
-        <v>6729038</v>
+        <v>6728823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395852</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395847</v>
+        <v>121395861</v>
       </c>
       <c r="B3" t="n">
-        <v>79193</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447471</v>
+        <v>447523</v>
       </c>
       <c r="R3" t="n">
-        <v>6729001</v>
+        <v>6729097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395864</v>
+        <v>121395847</v>
       </c>
       <c r="B4" t="n">
-        <v>78249</v>
+        <v>79196</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447448</v>
+        <v>447471</v>
       </c>
       <c r="R4" t="n">
-        <v>6728823</v>
+        <v>6729001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395861</v>
+        <v>121395864</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>78252</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447523</v>
+        <v>447448</v>
       </c>
       <c r="R5" t="n">
-        <v>6729097</v>
+        <v>6728823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395852</v>
+        <v>121395861</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447606</v>
+        <v>447523</v>
       </c>
       <c r="R2" t="n">
-        <v>6729038</v>
+        <v>6729097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395861</v>
+        <v>121395847</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>79196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447523</v>
+        <v>447471</v>
       </c>
       <c r="R3" t="n">
-        <v>6729097</v>
+        <v>6729001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395847</v>
+        <v>121395864</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>78252</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447471</v>
+        <v>447448</v>
       </c>
       <c r="R4" t="n">
-        <v>6729001</v>
+        <v>6728823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395864</v>
+        <v>121395852</v>
       </c>
       <c r="B5" t="n">
-        <v>78252</v>
+        <v>90713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447448</v>
+        <v>447606</v>
       </c>
       <c r="R5" t="n">
-        <v>6728823</v>
+        <v>6729038</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395861</v>
+        <v>121395847</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>79197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447523</v>
+        <v>447471</v>
       </c>
       <c r="R2" t="n">
-        <v>6729097</v>
+        <v>6729001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395847</v>
+        <v>121395861</v>
       </c>
       <c r="B3" t="n">
-        <v>79196</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447471</v>
+        <v>447523</v>
       </c>
       <c r="R3" t="n">
-        <v>6729001</v>
+        <v>6729097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121395864</v>
       </c>
       <c r="B4" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>121395852</v>
       </c>
       <c r="B5" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121395847</v>
       </c>
       <c r="B2" t="n">
-        <v>79197</v>
+        <v>79198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395861</v>
+        <v>121395864</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>78254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447523</v>
+        <v>447448</v>
       </c>
       <c r="R3" t="n">
-        <v>6729097</v>
+        <v>6728823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395864</v>
+        <v>121395861</v>
       </c>
       <c r="B4" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447448</v>
+        <v>447523</v>
       </c>
       <c r="R4" t="n">
-        <v>6728823</v>
+        <v>6729097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>121395852</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395864</v>
+        <v>121395852</v>
       </c>
       <c r="B3" t="n">
-        <v>78254</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447448</v>
+        <v>447606</v>
       </c>
       <c r="R3" t="n">
-        <v>6728823</v>
+        <v>6729038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395852</v>
+        <v>121395864</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>78254</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447606</v>
+        <v>447448</v>
       </c>
       <c r="R5" t="n">
-        <v>6729038</v>
+        <v>6728823</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395847</v>
+        <v>121395852</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447471</v>
+        <v>447606</v>
       </c>
       <c r="R2" t="n">
-        <v>6729001</v>
+        <v>6729038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395852</v>
+        <v>121395847</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>79198</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447606</v>
+        <v>447471</v>
       </c>
       <c r="R3" t="n">
-        <v>6729038</v>
+        <v>6729001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20098-2024 artfynd.xlsx
+++ b/artfynd/A 20098-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395852</v>
+        <v>121395864</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>78261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447606</v>
+        <v>447448</v>
       </c>
       <c r="R2" t="n">
-        <v>6729038</v>
+        <v>6728823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395847</v>
+        <v>121395852</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447471</v>
+        <v>447606</v>
       </c>
       <c r="R3" t="n">
-        <v>6729001</v>
+        <v>6729038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395861</v>
+        <v>121395847</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79205</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447523</v>
+        <v>447471</v>
       </c>
       <c r="R4" t="n">
-        <v>6729097</v>
+        <v>6729001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395864</v>
+        <v>121395861</v>
       </c>
       <c r="B5" t="n">
-        <v>78254</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447448</v>
+        <v>447523</v>
       </c>
       <c r="R5" t="n">
-        <v>6728823</v>
+        <v>6729097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
